--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-encounter.xlsx
@@ -274,7 +274,7 @@
   </si>
   <si>
     <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}</t>
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -299,10 +299,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -315,10 +315,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -338,7 +338,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -354,10 +354,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」(Risōsukontentsu no gengo)</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>「リソースコンテンツの言語」</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -366,7 +366,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」(Ningen no gengo.)</t>
+    <t>「人間の言語。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -386,10 +386,10 @@
 </t>
   </si>
   <si>
-    <t>「人間の解釈のためのリソースのテキスト要約」</t>
-  </si>
-  <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>人間の解釈のためのリソースのテキスト要約</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -412,13 +412,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」(Fukuma rete iru, inrain no risōsu)</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>「含まれている、インラインのリソース」</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -451,7 +451,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Encounter.extension:associatedEncounter</t>
@@ -481,7 +481,7 @@
     <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
   </si>
   <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -534,7 +534,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>「出会いの現状。」(Deai no genjou.)</t>
+    <t>「Encounter（診察、受診、入退院など）の現状。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-status|4.0.1</t>
@@ -593,7 +593,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -606,11 +606,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>「認識されなくても無視できない拡張機能」(Ninshiki sarenakutemo mushi dekinai kakuchou kinou)</t>
-  </si>
-  <si>
-    <t>「基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
-修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。」</t>
+    <t>認識されなくても無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>基本的な要素の定義に含まれない追加情報を表すために使用されることがあり、それによって、その要素自体または取り込んでいる要素の子孫の理解を修正する。修飾子要素は通常、否定または修飾を提供します。拡張機能の安全で管理しやすい使用を実現するために、定義および使用に厳しいガバナンスセットが適用されています。どの実装者でも拡張機能を定義できますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張子をチェックする必要があります。
+修飾子拡張機能は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味を変更することもできません）。</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -660,7 +660,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>出会いの分類。 (Deai no bunrui.)</t>
+    <t>Encounter（診察、受診、入退院など）の分類。 (Deai no bunrui.)</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
@@ -722,19 +722,19 @@
 </t>
   </si>
   <si>
-    <t>特定の種類の出会い (tokutei no shurui no deai)</t>
-  </si>
-  <si>
-    <t>「特定の出会いの種類（例：メール相談、手術日帰り、スキルド・ナーシング、リハビリテーション）」</t>
-  </si>
-  <si>
-    <t>「出会いをさらに分類する方法が多数存在するため、この要素は0から複数の値をとる。」</t>
+    <t>特定の種類のEncounter（診察、受診、入退院など） (tokutei no shurui no deai)</t>
+  </si>
+  <si>
+    <t>特定のEncounter（診察、受診、入退院など）の種類（例：メール相談、手術日帰り、スキルド・ナーシング、リハビリテーション）</t>
+  </si>
+  <si>
+    <t>Encounter（診察、受診、入退院など）をさらに分類する方法が多数存在するため、この要素は0から複数の値をとる。</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>出会いのタイプ。 (Deai no taipu.)</t>
+    <t>Encounter（診察、受診、入退院など）のタイプ。 (Deai no taipu.)</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-type</t>
@@ -770,10 +770,10 @@
     <t>Encounter.priority</t>
   </si>
   <si>
-    <t>「出会いの緊急性を示す」</t>
-  </si>
-  <si>
-    <t>出会いの緊急性を示します。</t>
+    <t>Encounter（診察、受診、入退院など）の緊急性を示す</t>
+  </si>
+  <si>
+    <t>Encounter（診察、受診、入退院など）の緊急性を示します。</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
@@ -827,10 +827,10 @@
 </t>
   </si>
   <si>
-    <t>「この遭遇が記録されるべきケアのエピソード」</t>
-  </si>
-  <si>
-    <t>「特定のエピソードの一部として特定のエンカウンターを分類する必要がある場合、このフィールドを使用する必要があります。この関連は、政府報告、問題追跡、共通の課題に関連するエンカウンターを特定の目的のためにグループ化するのに役立ちます。これらの関連は、通常、エピソードの後に作成され、新しいエンカウンターを追加するためにエピソードを編集するのではなく、入力時にグループ化されます（エピソードは数年にわたって広がる可能性があります）。」</t>
+    <t>この遭遇が記録されるべきケアのエピソード</t>
+  </si>
+  <si>
+    <t>特定のエピソードの一部として特定のエンカウンターを分類する必要がある場合、このフィールドを使用する必要があります。この関連は、政府報告、問題追跡、共通の課題に関連するエンカウンターを特定の目的のためにグループ化するのに役立ちます。これらの関連は、通常、エピソードの後に作成され、新しいエンカウンターを追加するためにエピソードを編集するのではなく、入力時にグループ化されます（エピソードは数年にわたって広がる可能性があります）。</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -853,10 +853,10 @@
 </t>
   </si>
   <si>
-    <t>この出会いを開始したサービスリクエスト</t>
-  </si>
-  <si>
-    <t>この出会いが満たす要請（例：紹介依頼や手続き要請）</t>
+    <t>このEncounter（診察、受診、入退院など）を開始したサービスリクエスト</t>
+  </si>
+  <si>
+    <t>このEncounter（診察、受診、入退院など）が満たす要請（例：紹介依頼や手続き要請）</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -871,7 +871,7 @@
     <t>「遭遇に関わった参加者のリスト」 (Souguu ni kakawatta sankasha no risuto)</t>
   </si>
   <si>
-    <t>「サービスを提供する責任を持つ人々のリスト」</t>
+    <t>サービスを提供する責任を持つ人々のリスト</t>
   </si>
   <si>
     <t>Event.performer</t>
@@ -895,10 +895,10 @@
     <t>Encounter.participant.type</t>
   </si>
   <si>
-    <t>「出会いにおける参加者の役割」</t>
-  </si>
-  <si>
-    <t>出会いにおける参加者の役割。</t>
+    <t>Encounter（診察、受診、入退院など）における参加者の役割</t>
+  </si>
+  <si>
+    <t>Encounter（診察、受診、入退院など）における参加者の役割。</t>
   </si>
   <si>
     <t>参加者タイプは、個人がどのようにエンカウントに参加するかを示します。それには、非開業者の参加者が含まれ、開業者にとってはこのエンカウントの文脈でアクションタイプを説明することが含まれます（例：入院医師、診療医師、翻訳者、相談医師）。これは、雇用、教育、免許などの用語から派生した機能的な役割である開業者の役割とは異なります。</t>
@@ -938,10 +938,10 @@
 </t>
   </si>
   <si>
-    <t>「患者以外に関与する人」</t>
-  </si>
-  <si>
-    <t>「患者以外に出会いに関わった人々。」(Kanja igai ni deai ni kakawatta hitobito.)</t>
+    <t>患者以外に関与する人</t>
+  </si>
+  <si>
+    <t>「患者以外にEncounter（診察、受診、入退院など）に関わった人々。」</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -963,10 +963,10 @@
 </t>
   </si>
   <si>
-    <t>「この出会いを予定した予約」(Kono deai o yotei shita yoyaku)</t>
-  </si>
-  <si>
-    <t>「この出会いを予定した約束。」</t>
+    <t>このEncounter（診察、受診、入退院など）を予定した予約</t>
+  </si>
+  <si>
+    <t>このEncounter（診察、受診、入退院など）を予定した約束。</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=FLFS].target[classCode=ENC, moodCode=APT]</t>
@@ -978,13 +978,13 @@
     <t>Encounter.period</t>
   </si>
   <si>
-    <t>出会いの始まりと終わりの時間</t>
-  </si>
-  <si>
-    <t>出会いの開始時刻と終了時刻。</t>
-  </si>
-  <si>
-    <t>「もし、まだ知られていなければ、期間の終わりは省略できます。」</t>
+    <t>Encounter（診察、受診、入退院など）の始まりと終わりの時間</t>
+  </si>
+  <si>
+    <t>Encounter（診察、受診、入退院など）の開始時刻と終了時刻。</t>
+  </si>
+  <si>
+    <t>もし、まだ知られていなければ、期間の終わりは省略できます。</t>
   </si>
   <si>
     <t>Event.occurrence[x]</t>
@@ -1006,13 +1006,13 @@
 </t>
   </si>
   <si>
-    <t>出会いが続いた時間（不在時間を差し引いた時間）</t>
+    <t>Encounter（診察、受診、入退院など）が続いた時間（不在時間を差し引いた時間）</t>
   </si>
   <si>
     <t>接触が続いた時間の量です。休暇中の時間は除かれます。</t>
   </si>
   <si>
-    <t>「休暇により、エンカウンター期間の時間が異なる場合があります。」</t>
+    <t>休暇により、エンカウンター期間の時間が異なる場合があります。</t>
   </si>
   <si>
     <t>.lengthOfStayQuantity</t>
@@ -1028,16 +1028,16 @@
 Admission diagnosis</t>
   </si>
   <si>
-    <t>「エンカウントが生じる理由がコード化されている」</t>
-  </si>
-  <si>
-    <t>出会いが起こる理由をコードとして表現します。入院に関しては、コード化された入院診断に使用できます。</t>
+    <t>エンカウントが生じる理由がコード化されている</t>
+  </si>
+  <si>
+    <t>Encounter（診察、受診、入退院など）が起こる理由をコードとして表現します。入院に関しては、コード化された入院診断に使用できます。</t>
   </si>
   <si>
     <t>主要な診断を知る必要があるシステムには、標準拡張子primaryDiagnosis（フラグではなく、シーケンス値である1 = 主要な診断）でマークされます。</t>
   </si>
   <si>
-    <t>出会いが起こる理由。</t>
+    <t>Encounter（診察、受診、入退院など）が起こる理由。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
@@ -1062,7 +1062,7 @@
 </t>
   </si>
   <si>
-    <t>出会いが生じた理由（参照）(Deai ga shoujita riyuu (sanshou))</t>
+    <t>Encounter（診察、受診、入退院など）が生じた理由（参照）(Deai ga shoujita riyuu (sanshou))</t>
   </si>
   <si>
     <t>Encounter.diagnosis</t>
@@ -1071,7 +1071,7 @@
     <t>この診察に関連する診断のリスト</t>
   </si>
   <si>
-    <t>「この対面に関連する診断リスト。」</t>
+    <t>この対面に関連する診断リスト。</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=RSON]</t>
@@ -1097,10 +1097,10 @@
 </t>
   </si>
   <si>
-    <t>「エンカウンターに関連する診断または処置」</t>
-  </si>
-  <si>
-    <t>「エンカウンターが発生する理由は、他のリソースからの情報を使用して指定されます。入院の場合、これは入院診断です。指標は通常、状態（evidence.detailで参照される他のリソースで）または手順です。」</t>
+    <t>エンカウンターに関連する診断または処置</t>
+  </si>
+  <si>
+    <t>エンカウンターが発生する理由は、他のリソースからの情報を使用して指定されます。入院の場合、これは入院診断です。指標は通常、状態（evidence.detailで参照される他のリソースで）またはプロシジャー（処置等）です。</t>
   </si>
   <si>
     <t>Event.reasonReference</t>
@@ -1118,7 +1118,7 @@
     <t>この診断に対する役割（入院、請求、退院など）</t>
   </si>
   <si>
-    <t>この診断が出会いの中で果たす役割（入院、請求、退院など）</t>
+    <t>この診断がEncounter（診察、受診、入退院など）の中で果たす役割（入院、請求、退院など）</t>
   </si>
   <si>
     <t>この状態が表す診断のタイプ。 (Kono jōtai ga arawasu shindan no taipu.)</t>
@@ -1137,7 +1137,7 @@
     <t>役割ごとの診断ランキング</t>
   </si>
   <si>
-    <t>「各役割タイプの診断ランキング」</t>
+    <t>各役割タイプの診断ランキング</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=RSON].priority</t>
@@ -1153,10 +1153,10 @@
     <t>このエンカウンターの請求に使用できるアカウントのセット</t>
   </si>
   <si>
-    <t>このインカウンターの請求に使用できるアカウントのセット。</t>
-  </si>
-  <si>
-    <t>請求システムは内部のビジネスルールに基づいて、出会いに関連する請求可能なアイテムを複数の参照されたアカウントに割り当てることができます。</t>
+    <t>このエンカウンターの請求に使用できるアカウントのセット。</t>
+  </si>
+  <si>
+    <t>請求システムは内部のビジネスルールに基づいて、Encounter（診察、受診、入退院など）に関連する請求可能なアイテムを複数の参照されたアカウントに割り当てることができます。</t>
   </si>
   <si>
     <t>.pertains.A_Account</t>
@@ -1165,10 +1165,10 @@
     <t>Encounter.hospitalization</t>
   </si>
   <si>
-    <t>「医療サービスの入院に関する詳細」</t>
-  </si>
-  <si>
-    <t>「医療サービスへの入院に関する詳細。」</t>
+    <t>医療サービスの入院に関する詳細</t>
+  </si>
+  <si>
+    <t>医療サービスへの入院に関する詳細。</t>
   </si>
   <si>
     <t>「エンカウンター」は入院期間だけでなく、外来診療、地域クリニック、高齢者施設などの文脈も含まれる場合があります。@@ -1190,10 +1190,10 @@
     <t>Encounter.hospitalization.preAdmissionIdentifier</t>
   </si>
   <si>
-    <t>事前入学識別子 (Jizen nyugaku shikibetsushi)</t>
-  </si>
-  <si>
-    <t>「入学前の識別子」(Nyūgaku mae no shikibetsu-shi)</t>
+    <t>事前入院identifier (Jizen nyugaku shikibetsushi)</t>
+  </si>
+  <si>
+    <t>「入院前のidentifier」</t>
   </si>
   <si>
     <t>PV1-5</t>
@@ -1206,10 +1206,10 @@
 </t>
   </si>
   <si>
-    <t>「入院前に患者がいた場所／組織」(nyūin zen ni kanja ga ita basho / soshiki)</t>
-  </si>
-  <si>
-    <t>「患者が入院する前に、どこの場所/組織から来たか。」</t>
+    <t>「入院前に患者がいた場所／組織」</t>
+  </si>
+  <si>
+    <t>患者が入院する前に、どこの場所/組織から来たか。</t>
   </si>
   <si>
     <t>.participation[typeCode=ORG].role</t>
@@ -1218,10 +1218,10 @@
     <t>Encounter.hospitalization.admitSource</t>
   </si>
   <si>
-    <t>「患者が入院した場所（医師の紹介、転院）」</t>
-  </si>
-  <si>
-    <t>「患者がどこから入院したのか（医師の紹介、転院）」</t>
+    <t>患者が入院した場所（医師の紹介、転院）</t>
+  </si>
+  <si>
+    <t>患者がどこから入院したのか（医師の紹介、転院）</t>
   </si>
   <si>
     <t>患者が入院した場所はどこですか。 (Kanja ga nyūin shita basho wa doko desu ka?)</t>
@@ -1242,7 +1242,7 @@
     <t>発生した再入院のタイプ（あれば）。値がない場合は、再入院として識別されていないことを意味します。</t>
   </si>
   <si>
-    <t>「この入院が再入院かどうか、そしてその理由が分かっている場合はなぜか。」</t>
+    <t>この入院が再入院かどうか、そしてその理由が分かっている場合はなぜか。</t>
   </si>
   <si>
     <t>この入院の再入院の理由。</t>
@@ -1269,7 +1269,7 @@
     <t>Used to track patient's diet restrictions and/or preference. For a complete description of the nutrition needs of a patient during their stay, one should use the nutritionOrder resource which links to Encounter.</t>
   </si>
   <si>
-    <t>「食品の好みを考慮して、医療、文化、倫理的観点から、提供要件に対応することができます。」</t>
+    <t>食品の好みを考慮して、医療、文化、倫理的観点から、提供要件に対応することができます。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-diet</t>
@@ -1308,7 +1308,7 @@
     <t>車椅子、翻訳者、ストレッチャー、など。</t>
   </si>
   <si>
-    <t>「この入院の機会に行われた特別な要求、特定の装置などの提供などがある場合は。」</t>
+    <t>この入院の機会に行われた特別な要求、特定の装置などの提供などがある場合は。</t>
   </si>
   <si>
     <t>特別な手配。</t>
@@ -1341,7 +1341,7 @@
     <t>Encounter.hospitalization.dischargeDisposition</t>
   </si>
   <si>
-    <t>「退院後の場所のカテゴリーまたは種類」</t>
+    <t>退院後の場所のカテゴリーまたは種類</t>
   </si>
   <si>
     <t>退院後の場所のカテゴリーまたは種類。</t>
@@ -1365,10 +1365,10 @@
     <t>患者が行った場所のリスト</t>
   </si>
   <si>
-    <t>「この接触中に患者が滞在した場所のリスト」</t>
-  </si>
-  <si>
-    <t>「エンカウント」には、場所の種類である「クライアントの自宅」のような場所の参照を明示することで、バーチャルなエンカウントを記録できます。また、エンカウントクラスは「バーチャル」である必要があります。」</t>
+    <t>この接触中に患者が滞在した場所のリスト</t>
+  </si>
+  <si>
+    <t>エンカウント」には、場所の種類である「クライアントの自宅」のような場所の参照を明示することで、バーチャルなエンカウントを記録できます。また、エンカウントクラスは「バーチャル」である必要があります。</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC]</t>
@@ -1390,10 +1390,10 @@
 </t>
   </si>
   <si>
-    <t>出会いの場所 (Deai no basho)</t>
-  </si>
-  <si>
-    <t>出会いが起こる場所。</t>
+    <t>Encounter（診察、受診、入退院など）の場所 (Deai no basho)</t>
+  </si>
+  <si>
+    <t>Encounter（診察、受診、入退院など）が起こる場所。</t>
   </si>
   <si>
     <t>Event.location</t>
@@ -1432,7 +1432,7 @@
     <t>場所の物理的なタイプ（通常は場所の階層のレベル、ベッドルームワードなど）</t>
   </si>
   <si>
-    <t>「これは、メッセージングまたはクエリを簡素化するために記録が必要なレベル（ベッド/病室/部屋など）を特定するために使用されます。」</t>
+    <t>これは、メッセージングまたはクエリを簡素化するために記録が必要なレベル（ベッド/病室/部屋など）を特定するために使用されます。</t>
   </si>
   <si>
     <t>この情報は、エンカウンターリソースの理解とメッセージングまたはクエリの処理をサポートするために、ロケーションリソースからデノーマライズされています。
@@ -1448,7 +1448,7 @@
     <t>Encounter.location.period</t>
   </si>
   <si>
-    <t>「患者が場所にいた期間」</t>
+    <t>患者が場所にいた期間</t>
   </si>
   <si>
     <t>"患者が場所にいた期間。"</t>
@@ -1461,10 +1461,10 @@
 </t>
   </si>
   <si>
-    <t>この出会いに責任を持つ組織（施設）</t>
-  </si>
-  <si>
-    <t>このエンカウンターのサービスを主に担当する組織。これは患者の記録にある組織と同じかもしれませんが、外部組織からサービスを提供するアクターがいる場合など、別の組織である可能性もあります(別途請求される可能性があります)。大腸内視鏡検査の簡略化されたエンカウンターのバンドルを参照してください。</t>
+    <t>このEncounter（診察、受診、入退院など）に責任を持つ組織（施設）</t>
+  </si>
+  <si>
+    <t>このエンカウンターのサービスを主に担当する組織。これは患者の記録にある組織と同じかもしれませんが、外部組織からサービスを提供するアクターがいる場合など、別の組織である可能性もあります(別途請求される可能性があります)。大腸内視鏡検査の簡略化されたエンカウンターのBundleを参照してください。</t>
   </si>
   <si>
     <t>.particiaption[typeCode=PFM].role</t>
@@ -1480,13 +1480,13 @@
 </t>
   </si>
   <si>
-    <t>「もう一度の出会い。この出会いは一部である。」</t>
-  </si>
-  <si>
-    <t>この出会いが一部である、別の出会い（手続き的にも時間的にも）。</t>
-  </si>
-  <si>
-    <t>「これは、子供の経験を母親の経験に関連付けるためにも使用されます。詳細については、患者リソースのノートセクションを参照してください。」</t>
+    <t>もう一度のEncounter（診察、受診、入退院など）。このEncounter（診察、受診、入退院など）は一部である。</t>
+  </si>
+  <si>
+    <t>このEncounter（診察、受診、入退院など）が一部である、別のEncounter（診察、受診、入退院など）（手続き的にも時間的にも）。</t>
+  </si>
+  <si>
+    <t>これは、子供の経験を母親の経験に関連付けるためにも使用されます。詳細については、患者リソースのノートセクションを参照してください。</t>
   </si>
   <si>
     <t>Event.partOf</t>
